--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260716.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260716.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>332,950,632</t>
+          <t>67,753,026</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>67,753,026</t>
+          <t>2,283,344</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,283,344</t>
+          <t>332,950,632</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>16,711,626</t>
+          <t>66,134,074</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>66,134,074</t>
+          <t>16,711,626</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>245,296,557</t>
+          <t>1,249,590</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,249,590</t>
+          <t>245,296,557</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>23,814,245</t>
+          <t>7,527,784</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,527,784</t>
+          <t>23,814,245</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
